--- a/tamu_data/evals/golden_sets/CSCE_25gradcourses_nonrecursive.xlsx
+++ b/tamu_data/evals/golden_sets/CSCE_25gradcourses_nonrecursive.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,16 @@
           <t>run:CSCE_25gradcourses_20260418_20260418_090845</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>run:cs250_ov50_20260425_214025</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>run:cs250_ov50_ragas_20260426_002345</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="86.40000000000001" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -568,6 +578,16 @@
           <t>CSCE 611 §? 0.68, CSCE 611 §? 0.54</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.71, CSCE 611 §? 0.70, CSCE 611 §? 0.62, CSCE 611 §? 0.59, CSCE 611 §? 0.57, CSCE 611 §? 0.52</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.71, CSCE 611 §? 0.70, CSCE 611 §? 0.62, CSCE 611 §? 0.59, CSCE 611 §? 0.57, CSCE 611 §? 0.52</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="172.8" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -617,6 +637,16 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>CSCE 612 §? 0.89, CSCE 612 §? 0.65</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>CSCE 612 §? 0.86, CSCE 612 §? 0.84</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>CSCE 612 §? 0.86, CSCE 612 §? 0.84</t>
         </is>
       </c>
     </row>
@@ -671,6 +701,16 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>CSCE 669 §? 0.80, CSCE 669 §? 0.51</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.71, CSCE 669 §? 0.70</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.71, CSCE 669 §? 0.70</t>
         </is>
       </c>
     </row>
@@ -726,6 +766,16 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>CSCE 665 §? 0.93, CSCE 665 §? 0.79</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.93, CSCE 665 §? 0.81</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.93, CSCE 665 §? 0.81</t>
         </is>
       </c>
     </row>
@@ -785,6 +835,16 @@
           <t>CSCE 670 §? 0.89, CSCE 670 §? 0.62</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.82, CSCE 670 §? 0.67</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.82, CSCE 670 §? 0.67</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="144" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -836,6 +896,16 @@
           <t>CSCE 676 §? 0.90, CSCE 676 §? 0.60</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>CSCE 676 §? 0.86, CSCE 676 §? 0.55</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CSCE 676 §? 0.86, CSCE 676 §? 0.55</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="273.6" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -888,6 +958,16 @@
           <t>CSCE 672 §? 0.82, CSCE 672 §? 0.62</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.76, CSCE 672 §? 0.67</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.76, CSCE 672 §? 0.67</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="172.8" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -937,6 +1017,16 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>CSCE 608 §? 0.89, CSCE 608 §? 0.62</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.87, CSCE 608 §? 0.66</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.87, CSCE 608 §? 0.66</t>
         </is>
       </c>
     </row>
@@ -995,6 +1085,16 @@
           <t>CSCE 624 §? 0.84, CSCE 624 §? 0.74</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>CSCE 624 §? 0.70, CSCE 624 §? 0.70, CSCE 624 §? 0.70</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>CSCE 624 §? 0.70, CSCE 624 §? 0.70, CSCE 624 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="216" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1048,6 +1148,16 @@
           <t>CSCE 629 §? 0.85, CSCE 629 §? 0.52</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.88, CSCE 629 §? 0.60</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.88, CSCE 629 §? 0.60</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="158.4" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1097,6 +1207,16 @@
       <c r="L12" t="inlineStr">
         <is>
           <t>CSCE 638 §? 0.58, CSCE 638 §? 0.55</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.67, CSCE 638 §? 0.62</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.67, CSCE 638 §? 0.62</t>
         </is>
       </c>
     </row>
@@ -1162,6 +1282,16 @@
           <t>CSCE 656 §? 0.80, CSCE 656 §? 0.59</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>CSCE 656 §? 0.61, CSCE 656 §? 0.52, CSCE 656 §? 0.52</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CSCE 656 §? 0.61, CSCE 656 §? 0.52, CSCE 656 §? 0.52</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="201.6" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1212,6 +1342,16 @@
       <c r="L14" t="inlineStr">
         <is>
           <t>CSCE 665 §? 0.75, CSCE 665 §? 0.54</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.69, CSCE 665 §? 0.55, CSCE 665 §? 0.55</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.69, CSCE 665 §? 0.55, CSCE 665 §? 0.55</t>
         </is>
       </c>
     </row>
@@ -1270,6 +1410,16 @@
           <t>CSCE 641 §? 0.79, CSCE 641 §? 0.61</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>CSCE 641 §? 0.79, CSCE 641 §? 0.78</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>CSCE 641 §? 0.79, CSCE 641 §? 0.78</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="302.4" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1325,6 +1475,16 @@
           <t>CSCE 672 §? 0.80, CSCE 672 §? 0.68</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.71</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.71</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="187.2" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1380,6 +1540,16 @@
           <t>CSCE 608 §? 0.66, CSCE 608 §? 0.47</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.67, CSCE 608 §? 0.63</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.67, CSCE 608 §? 0.63</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="158.4" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -1430,6 +1600,16 @@
           <t>CSCE 605 §? 0.68, CSCE 681 §? 0.63, CSCE 713 §? 0.63, CSCE 629 §? 0.62, CSCE 681 §? 0.59, CSCE 652 §? 0.59, CSCE 614 §? 0.59, ISEN 620 §? 0.59, CSCE 635 §? 0.57, ISEN 620 §? 0.57</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.62, CSCE 681 §? 0.61, CSCE 681 §? 0.61, CSCE 681 §? 0.60, CSCE 632 §? 0.60, CSCE 629 §? 0.57, ISEN 441 §? 0.57, CSCE 624 §? 0.55, CSCE 111 §? 0.54, CSCE 111 §? 0.54</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.62, CSCE 681 §? 0.61, CSCE 681 §? 0.61, CSCE 681 §? 0.60, CSCE 632 §? 0.60, CSCE 629 §? 0.57, ISEN 441 §? 0.57, CSCE 624 §? 0.55, CSCE 111 §? 0.54, CSCE 111 §? 0.54</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="86.40000000000001" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -1480,6 +1660,16 @@
           <t>CSCE 672 §? 0.75, CSCE 672 §? 0.52</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.75, CSCE 672 §? 0.73, CSCE 672 §? 0.70</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.75, CSCE 672 §? 0.73, CSCE 672 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="86.40000000000001" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1530,6 +1720,16 @@
           <t>CSCE 652 §? 0.55, CSCE 652 §? 0.50, CSCE 605 §? 0.47, CSCE 605 §? 0.46, CSCE 676 §? 0.45, CSCE 632 §? 0.44, ISEN 620 §? 0.44, ISEN 620 §? 0.43, CSCE 713 §? 0.43, CSCE 633 §? 0.41</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.61, CSCE 629 §? 0.59, ISEN 441 §? 0.58, CSCE 629 §? 0.58, CSCE 652 §? 0.56</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.61, CSCE 629 §? 0.59, ISEN 441 §? 0.58, CSCE 629 §? 0.58, CSCE 652 §? 0.56</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="100.8" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -1580,6 +1780,16 @@
           <t>CSCE 638 §? 0.72, CSCE 670 §? 0.61</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.71, CSCE 638 §? 0.71, CSCE 638 §? 0.70, CSCE 670 §? 0.70, CSCE 638 §? 0.68, CSCE 638 §? 0.68</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.71, CSCE 638 §? 0.71, CSCE 638 §? 0.70, CSCE 670 §? 0.70, CSCE 638 §? 0.68, CSCE 638 §? 0.68</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="129.6" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -1630,6 +1840,16 @@
           <t>CSCE 681 §? 0.77, CSCE 672 §? 0.51</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.75, CSCE 681 §? 0.69</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.75, CSCE 681 §? 0.69</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="144" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -1680,6 +1900,16 @@
           <t>ISEN 620 §? 0.49, CSCE 614 §? 0.48, CSCE 681 §? 0.47, CSCE 633 §? 0.46, CSCE 681 §? 0.44, CSCE 605 §? 0.43, CSCE 608 §? 0.43, CSCE 605 §? 0.41, ISEN 620 §? 0.41, CSCE 605 §? 0.40</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>CSCE 635 §? 0.57, CSCE 656 §? 0.55, CSCE 421 §? 0.54, CSCE 633 §? 0.52, CSCE 633 §? 0.52, CSCE 672 §? 0.51, CSCE 672 §? 0.51, CSCE 672 §? 0.51, CSCE 672 §? 0.50, CSCE 633 §? 0.50</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>CSCE 635 §? 0.57, CSCE 656 §? 0.55, CSCE 421 §? 0.54, CSCE 633 §? 0.52, CSCE 633 §? 0.52, CSCE 672 §? 0.51, CSCE 672 §? 0.51, CSCE 672 §? 0.51, CSCE 672 §? 0.50, CSCE 633 §? 0.50</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="86.40000000000001" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -1730,6 +1960,16 @@
           <t>CSCE 679 §? 0.81, CSCE 679 §? 0.55</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>CSCE 679 §? 0.81, CSCE 679 §? 0.81, CSCE 679 §? 0.80, CSCE 679 §? 0.77</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>CSCE 679 §? 0.81, CSCE 679 §? 0.81, CSCE 679 §? 0.80, CSCE 679 §? 0.77</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28.8" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -1778,6 +2018,16 @@
       <c r="L25" t="inlineStr">
         <is>
           <t>CSCE 629 §? 0.74, CSCE 629 §? 0.70</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.78, CSCE 629 §? 0.70, CSCE 629 §? 0.57, CSCE 629 §? 0.55</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.78, CSCE 629 §? 0.70, CSCE 629 §? 0.57, CSCE 629 §? 0.55</t>
         </is>
       </c>
     </row>
@@ -1836,6 +2086,16 @@
           <t>CSCE 608 §? 0.88, CSCE 608 §? 0.41</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.73, CSCE 608 §? 0.56</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.73, CSCE 608 §? 0.56</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="43.2" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -1884,6 +2144,16 @@
       <c r="L27" t="inlineStr">
         <is>
           <t>CSCE 633 §? 0.71, CSCE 633 §? 0.47</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.75, CSCE 633 §? 0.47</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.75, CSCE 633 §? 0.47</t>
         </is>
       </c>
     </row>
@@ -1938,6 +2208,16 @@
       <c r="L28" t="inlineStr">
         <is>
           <t>CSCE 633 §? 0.84, CSCE 633 §? 0.57</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.76, CSCE 633 §? 0.60</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.76, CSCE 633 §? 0.60</t>
         </is>
       </c>
     </row>
@@ -1996,6 +2276,16 @@
           <t>CSCE 665 §? 0.85, CSCE 665 §? 0.59</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.80, CSCE 665 §? 0.75</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.80, CSCE 665 §? 0.75</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="144" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -2050,6 +2340,16 @@
           <t>CSCE 669 §? 0.79, CSCE 669 §? 0.48</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.71, CSCE 669 §? 0.66</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.71, CSCE 669 §? 0.66</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="144" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -2104,6 +2404,16 @@
           <t>CSCE 665 §? 0.84, CSCE 665 §? 0.70</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.76, CSCE 665 §? 0.71, CSCE 665 §? 0.64</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.76, CSCE 665 §? 0.71, CSCE 665 §? 0.64</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="57.6" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -2154,6 +2464,16 @@
           <t>CSCE 608 §? 0.91, CSCE 608 §? 0.64</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.88, CSCE 608 §? 0.70</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.88, CSCE 608 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="72" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -2202,6 +2522,16 @@
       <c r="L33" t="inlineStr">
         <is>
           <t>CSCE 681 §? 0.87, CSCE 681 §? 0.50</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.72, CSCE 681 §? 0.70</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.72, CSCE 681 §? 0.70</t>
         </is>
       </c>
     </row>
@@ -2258,6 +2588,16 @@
           <t>CSCE 611 §? 0.80, CSCE 611 §? 0.76</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.79, CSCE 611 §? 0.74, CSCE 611 §? 0.69, CSCE 611 §? 0.68, CSCE 611 §? 0.68</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.79, CSCE 611 §? 0.74, CSCE 611 §? 0.69, CSCE 611 §? 0.68, CSCE 611 §? 0.68</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="244.8" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -2310,6 +2650,16 @@
       <c r="L35" t="inlineStr">
         <is>
           <t>CSCE 670 §? 0.72, CSCE 670 §? 0.71</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.68, CSCE 670 §? 0.65, CSCE 670 §? 0.59</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.68, CSCE 670 §? 0.65, CSCE 670 §? 0.59</t>
         </is>
       </c>
     </row>
@@ -2368,6 +2718,16 @@
           <t>CSCE 632 §? 0.80, CSCE 632 §? 0.77, CSCE 632 §? 0.73</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>CSCE 632 §? 0.73, CSCE 632 §? 0.71, CSCE 632 §? 0.69, CSCE 632 §? 0.65</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>CSCE 632 §? 0.73, CSCE 632 §? 0.71, CSCE 632 §? 0.69, CSCE 632 §? 0.65</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="201.6" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -2422,6 +2782,16 @@
           <t>CSCE 669 §? 0.85, CSCE 669 §? 0.78</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.78, CSCE 669 §? 0.55</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.78, CSCE 669 §? 0.55</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="259.2" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -2474,6 +2844,16 @@
       <c r="L38" t="inlineStr">
         <is>
           <t>CSCE 670 §? 0.79, CSCE 670 §? 0.46</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.80, CSCE 670 §? 0.56</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.80, CSCE 670 §? 0.56</t>
         </is>
       </c>
     </row>

--- a/tamu_data/evals/golden_sets/CSCE_25gradcourses_nonrecursive.xlsx
+++ b/tamu_data/evals/golden_sets/CSCE_25gradcourses_nonrecursive.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,26 @@
           <t>run:cs250_ov50_ragas_20260426_002345</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>run:bm25_semantic_general_20260426_014722</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>run:bm25_semantic_general</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>run:chunk_500t_100o_20260426_20260426_025514</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>run:chunk_500t_100o_trimmed_20260426_20260426_031556</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="86.40000000000001" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -588,6 +608,29 @@
           <t>CSCE 611 §? 0.71, CSCE 611 §? 0.70, CSCE 611 §? 0.62, CSCE 611 §? 0.59, CSCE 611 §? 0.57, CSCE 611 §? 0.52</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.73, CSCE 611 §? 0.69, CSCE 611 §? 0.62, CSCE 611 §? 0.61, CSCE 611 §? 0.59, CSCE 611 §? 0.58</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>In the beginning of CSCE 611 (Section 600, Spring 2026), the course covers the following topics:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 5].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 5].
+*   **Week 3:** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 5].</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.75, CSCE 611 §? 0.74</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.75, CSCE 611 §? 0.62</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="172.8" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -647,6 +690,32 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>CSCE 612 §? 0.86, CSCE 612 §? 0.84</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CSCE 612 §? 0.85, CSCE 612 §? 0.83</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CSCE 612, Section 600, "Applied Networks and Distributed Processing," focuses on the fundamentals of network design and protocol analysis within the context of computer communications [Source 1, 2].
+The course blends theoretical fundamentals with practical programming and engineering perspectives. Key topics include network architecture, principles of network engineering, and applying layered architecture principles to analyze real networks. Lab exercises emphasize protocol understanding and programming [Source 2].
+**Prerequisites**:
+*   Graduate classification [Source 2]
+*   CSCE 313 [Source 2]
+Knowledge of UNIX and C programming is helpful but not required [Source 2]. This course is stacked with CSCE 463, and graduate students in CSCE 612 will have additional requirements in assignments [Source 2].
+The provided context does not contain information regarding grading for this course.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CSCE 612 §? 0.89, CSCE 612 §? 0.89</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>CSCE 612 §? 0.89, CSCE 612 §? 0.59</t>
         </is>
       </c>
     </row>
@@ -711,6 +780,30 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>CSCE 669 §? 0.71, CSCE 669 §? 0.70</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.72, CSCE 669 §? 0.62</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 1].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.84, CSCE 669 §? 0.59</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.84, CSCE 669 §? 0.59</t>
         </is>
       </c>
     </row>
@@ -776,6 +869,31 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>CSCE 665 §? 0.93, CSCE 665 §? 0.81</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.91, CSCE 665 §? 0.84</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CSCE 665 will introduce various modern topics in computer and network security, including [Source 1, 2]:
+*   **Basic network &amp; system security:** e.g., software security, malware, botnet, intrusion detection [Source 1]
+*   **Security in a software-defined world:** e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security [Source 1]
+*   **Mobile &amp; IoT security:** e.g., smartphone security, Alexa and voice app security [Source 1, 2]
+*   **Web and Web3 security:** e.g., traditional web security, spam, Web3 (DeFi, blockchain) security [Source 1, 2]
+*   **AI/LLM security:** e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI [Source 2]</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.93, CSCE 665 §? 0.79</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.93, CSCE 665 §? 0.79</t>
         </is>
       </c>
     </row>
@@ -845,6 +963,51 @@
           <t>CSCE 670 §? 0.82, CSCE 670 §? 0.67</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.82, CSCE 670 §? 0.69, CSCE 670 §? 0.62, CSCE 670 §? 0.59, CSCE 670 §? 0.59</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CSCE 670 (Section 600) covers the following topics [Source 1, 2, 4, 5]:
+**Course Purpose and Catalog Description:**
+The course focuses on the representation, storage, and access to very large multimedia document collections. It covers fundamental data structures and algorithms of information storage and retrieval systems, as well as techniques to design and evaluate complete retrieval systems. This includes algorithms for indexing, compressing, and querying very large collections [Source 1, 2].
+**Key Topics and Learning Outcomes:**
+Upon completion, students will be able to:
+*   Define and explain key concepts and models relevant to web search, such as text indexing, retrieval models, evaluation, Web crawling, link-based algorithms (e.g., PageRank), and learning to rank [Source 2].
+*   Define and explain key concepts and models relevant to recommender systems, including collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 2, 3].
+*   Design, implement, and evaluate the core algorithms for fully functional web search and recommendation systems [Source 2, 3].
+*   Identify salient features and apply recent research results in web search and recommender systems, including adversarial information retrieval and neural models of retrieval and recommendation [Source 3].
+**Course Schedule (Topics by Week):**
+*   **Week 1:** Course Overview; Boolean Retrieval [Source 4]
+*   **Week 2:** TF-IDF; Vector Space Model; BM25 [Source 4]
+*   **Week 3:** Link Analysis [Source 4]
+*   **Week 4:** Evaluation of Search Engines [Source 4]
+*   **Week 5:** Learning to Rank [Source 4]
+*   **Week 6:** Recommender Systems (Content-Based; Collaborative Filtering) [Source 4]
+*   **Week 7:** Recommender Systems (Matrix Factorization; Bayesian Personalized Ranking) [Source 4]
+*   **Week 8:** word2vec; Neural Ranking [Source 4, 5]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 5]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 5]
+*   **Week 12:** Large Language Models Basics [Source 5]
+*   **Week 13:** Large Language Models with Search Engines [Source 5]
+*   **Week 14:** Large Language Models for Ranking and Recommendation [Source 5]
+*   **Week 15:** Wrap-up; Project Presentations [Source 5]
+**Prerequisites:**
+CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.86, CSCE 670 §? 0.68</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.86, CSCE 670 §? 0.68</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="144" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -906,6 +1069,35 @@
           <t>CSCE 676 §? 0.86, CSCE 676 §? 0.55</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>CSCE 676 §? 0.86, CSCE 676 §? 0.54</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CSCE 676, Section 600, titled "Data Mining and Analysis," provides a broad overview of data mining, integrating concepts from machine learning and statistics [Source 1].
+Key topics covered include:
+*   Exploratory data analysis [Source 1]
+*   Pattern mining [Source 1]
+*   Clustering and classification [Source 1]
+*   Applications to scientific and online data [Source 1]
+*   Data preparation, normalization, dimensionality reduction, and text mining [Source 2]
+*   Data mining algorithms such as associate rules, clustering, and anomaly detection [Source 2]
+*   Recent research in data mining, including graph mining and large-scale mining [Source 2]
+Students are expected to have previous exposure to basic probability, statistics, algorithms, and data structures, and be able to design and develop large programs and learn new software libraries independently [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CSCE 676 §? 0.88, CSCE 676 §? 0.88, CSCE 676 §? 0.87</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>CSCE 676 §? 0.88, CSCE 676 §? 0.57</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="273.6" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -968,6 +1160,45 @@
           <t>CSCE 672 §? 0.76, CSCE 672 §? 0.67</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.73, CSCE 672 §? 0.66, CSCE 672 §? 0.65, CSCE 672 §? 0.64</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>For CSCE 672, Section 600, titled "Computer Supported Collaborative Work," you should expect to engage with the design, implementation, and use of technical systems that support people working cooperatively [Source 3]. The course draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1, 3].
+**Key Topics and Learning Outcomes:**
+Throughout the course, you will learn to:
+*   Describe the history of collaborative software environments [Source 1].
+*   Prioritize issues and identify trade-offs in designing collaborative software [Source 1].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1].
+*   Analyze use contexts in terms of social processes, time, place, and resources [Source 1, 2].
+*   Assess the need for reciprocity, critical mass, and exception handling for collaborative applications [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Specific weekly topics include collaborative decision making, voting models, meeting capture, crowdsourcing, online communities, shared user history, collaborative search and design, software supporting social skill development, collaboration in online games, and supporting software teams [Source 4].
+**Prerequisites:**
+To enroll in CSCE 672, you must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F. A specific late work policy for write-ups states that 50% is immediately deducted if turned in late, with an additional 5% deducted per day [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.80, CSCE 672 §? 0.66</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.80, CSCE 672 §? 0.66</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="172.8" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -1027,6 +1258,33 @@
       <c r="N9" t="inlineStr">
         <is>
           <t>CSCE 608 §? 0.87, CSCE 608 §? 0.66</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.86, CSCE 608 §? 0.71</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CSCE 608, Section 600, titled "Database Systems," covers database modeling techniques, expressiveness in query languages (including knowledge representation), manipulation languages data models, physical data organization, relational database design theory, query processing, transaction management and recovery, and distributed data management [Source 1, 2].
+Upon completion of the course, learners will be able to:
+*   Understand the fundamentals of database design
+*   Develop database systems for applications
+*   Understand relational database theory
+*   Master efficient query processing techniques
+*   Deal with system issues related to database systems [Source 2]
+The prerequisite for this course is CSCE 310 or approval of the Instructor [Source 1, 2]. The grading policy is mentioned but not detailed in the provided context [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.89, CSCE 608 §? 0.62</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.89, CSCE 608 §? 0.62</t>
         </is>
       </c>
     </row>
@@ -1095,6 +1353,34 @@
           <t>CSCE 624 §? 0.70, CSCE 624 §? 0.70, CSCE 624 §? 0.70</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>CSCE 624 §? 0.74, CSCE 624 §? 0.64, CSCE 624 §? 0.59</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>To take CSCE 624 (Section 600), you should have:
+*   **Prerequisite/Corequisite:** Graduate classification [Source 1, 2, 3].
+*   **Expected Knowledge:** General graduate-level knowledge in computer science [Source 1].
+Familiarity with at least one of the following is helpful but not strictly required:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 1]
+Students from related disciplines (e.g., engineering, HCI, data science) are welcome and have historically performed well in the course [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CSCE 624 §? 0.78, CSCE 624 §? 0.73</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>CSCE 624 §? 0.78, CSCE 624 §? 0.73</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="216" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1158,6 +1444,35 @@
           <t>CSCE 629 §? 0.88, CSCE 629 §? 0.60</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.86, CSCE 629 §? 0.57</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CSCE 629, Section 600, titled "Analysis of Algorithms," is offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Topics:**
+This 3-credit hour course focuses on concrete algorithm design and analysis. Key topics include abstract models for analyzing problem complexity, NP-Completeness, and approximation and probabilistic algorithms [Source 1]. Upon completion, students will be able to explain fundamental algorithms, select appropriate algorithms for problems, analyze correctness, runtime, and space complexity, design new algorithms, and recognize intractable problems by proving undecidability or NP-hardness [Source 2].
+**Prerequisites:**
+The prerequisite for this course is graduate classification [Source 1, 2].
+**Instructor and Meeting Times:**
+The instructor is Andreas Klappenecker. The class meets on Tuesdays and Thursdays from 11:10 am to 12:25 pm in HRBB 124 [Source 1].
+**Required Textbook:**
+The required textbook is "Introduction to Algorithms, fourth edition" by Thomas H. Cormen, Charles E. Leiserson, Ronald L. Rivest, and Clifford Stein (ISBN: 9780262367509) [Source 2].
+Information regarding grading is not available in the provided context.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.89, CSCE 629 §? 0.88</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.88, CSCE 629 §? 0.59</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="158.4" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1217,6 +1532,37 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>CSCE 638 §? 0.67, CSCE 638 §? 0.62</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.65, CSCE 638 §? 0.60, CSCE 638 §? 0.55, CSCE 638 §? 0.54</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638, Section 600, "Natural Language Processing: Foundations and Techniques," would be beneficial for someone wanting to work with Large Language Models (LLMs) [Source 1].
+The course covers several topics directly relevant to LLMs and their applications:
+*   **Language Models** [Source 1, 3]
+*   **Transformers** [Source 2, 3]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2, 3]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2, 3]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2, 3]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle challenges in natural language processing [Source 4]. These skills and topics are directly applicable to careers involving the development, deployment, and analysis of Large Language Models in industry.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.67, CSCE 638 §? 0.63</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.67, CSCE 638 §? 0.63</t>
         </is>
       </c>
     </row>
@@ -1292,6 +1638,39 @@
           <t>CSCE 656 §? 0.61, CSCE 656 §? 0.52, CSCE 656 §? 0.52</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>CSCE 656 §? 0.62, CSCE 656 §? 0.57, CSCE 656 §? 0.55</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600) covers both interactive media design and digital rights/policy topics.
+Based on the weekly schedule, a significant portion of the course focuses on interactive media design aspects, including:
+*   Designing software for immersion, agency, and transformation [Source 3]
+*   Interactive media and computer characters [Source 3]
+*   Interactive text and social media [Source 3]
+*   Bridging physical and digital media [Source 3]
+*   Audio, music, speech, recorded, and authored video [Source 3]
+*   Games and automatic narrative control [Source 3]
+However, the course also dedicates several weeks to digital rights and policy, such as:
+*   Digital rights management [Source 3]
+*   Property rights and issues [Source 3]
+*   Software licenses and intellectual property [Source 3]
+*   Evaluating policy effects [Source 3]
+Therefore, while a substantial part of the course aligns with your interest in interactive media design, you would also cover digital rights and policy topics [Source 3].</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CSCE 656 §? 0.64, CSCE 656 §? 0.51</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>CSCE 656 §? 0.64, CSCE 656 §? 0.51</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="201.6" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1352,6 +1731,32 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>CSCE 665 §? 0.69, CSCE 665 §? 0.55, CSCE 665 §? 0.55</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.66, CSCE 665 §? 0.56</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, section 600, would be a strong foundation if you are looking to specialize in real-world software or cloud security.
+The course provides a thorough grounding in computer and network security, suitable for students interested in "real-world security issues/techniques" [Source 1].
+**Career Relevance:**
+The course content directly addresses topics relevant to industry applications in software and cloud security:
+*   **Software Security:** It covers "Basic network &amp; system security: e.g., software security, malware, botnet, intrusion detection" [Source 1].
+*   **Cloud Security:** It includes "Security in a software-defined world: e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security" [Source 1].
+Upon completion, learners will be able to "Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks" and "Demonstrate a practical working knowledge of offensive and/or defensive techniques," which are valuable skills for these specializations [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.75, CSCE 665 §? 0.53</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.75, CSCE 665 §? 0.53</t>
         </is>
       </c>
     </row>
@@ -1420,6 +1825,34 @@
           <t>CSCE 641 §? 0.79, CSCE 641 §? 0.78</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>CSCE 641 §? 0.78, CSCE 641 §? 0.75, CSCE 641 §? 0.70, CSCE 641 §? 0.64</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [3].
+Key topics and skills relevant to these careers include:
+*   **Practical Image Synthesis Systems**: The course focuses on the application of rendering principles in practical image synthesis systems [1, 3].
+*   **Core Rendering Algorithms**: Students will implement core rendering algorithms such as ray tracing, direct illumination, and global illumination methods [1].
+*   **Physically Based Rendering System Design**: Learners will design and implement a physically based rendering system or rendering component [1, 4].
+*   **3D Object Representation and Techniques**: The course covers the representation of 3-dimensional objects (polyhedral, curved surfaces, volumetric, CSG models), hidden surface/edge removal, volume rendering, illumination, shading, antialiasing, ray tracing, radiosity, and animation [2, 3].
+*   **Practical Experience**: The course offers practical experience with state-of-the-art graphics hardware and software [3].
+These skills are directly applicable to developing graphics engines, tools, and content for games and other graphics-intensive applications.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CSCE 641 §? 0.82, CSCE 641 §? 0.70</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>CSCE 641 §? 0.82, CSCE 641 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="302.4" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1485,6 +1918,38 @@
           <t>CSCE 672 §? 0.75, CSCE 672 §? 0.71</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.76, CSCE 672 §? 0.70, CSCE 672 §? 0.63, CSCE 672 §? 0.54</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Computer Supported Collaborative Work), Section 600, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications [Source 2].
+The course covers the design, implementation, and use of technical systems that support people working cooperatively, drawing from the research area of Computer Supported Cooperative Work (CSCW) [Source 2, 1]. It includes current theoretical, practical, technical, and social issues in CSCW [Source 1].
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 3].
+Key topics covered include:
+*   Collaborative decision making [Source 4].
+*   Crowdsourcing and its issues [Source 4].
+*   Online communities and virtual teams [Source 4].
+*   Collaborative search and design [Source 4].
+*   Supporting software teams [Source 4].
+A significant portion of the grade (35%) is dedicated to a team project, which likely involves practical application [Source 3]. The course also requires online papers from conferences and journals as resources [Source 3].</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.80, CSCE 672 §? 0.67</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.80, CSCE 672 §? 0.67</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="187.2" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1550,6 +2015,36 @@
           <t>CSCE 608 §? 0.67, CSCE 608 §? 0.63</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.67, CSCE 608 §? 0.65</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems. The course aims for learners to be able to "develop database systems for applications" [Source 1].
+Key topics include:
+*   Database modeling techniques [Source 2]
+*   Expressiveness in query languages [Source 2]
+*   Manipulation languages data models [Source 2]
+*   Physical data organization [Source 2]
+*   Relational database design theory [Source 2]
+*   Query processing [Source 2]
+*   Transaction management and recovery [Source 2]
+*   Distributed data management [Source 2]
+Upon completion, students should also "master efficient query processing techniques" and "deal with system issues related to database systems" [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.75, CSCE 608 §? 0.53</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.75, CSCE 608 §? 0.53</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="158.4" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -1610,6 +2105,31 @@
           <t>CSCE 681 §? 0.62, CSCE 681 §? 0.61, CSCE 681 §? 0.61, CSCE 681 §? 0.60, CSCE 632 §? 0.60, CSCE 629 §? 0.57, ISEN 441 §? 0.57, CSCE 624 §? 0.55, CSCE 111 §? 0.54, CSCE 111 §? 0.54</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.62, CSCE 681 §? 0.61, CSCE 681 §? 0.61, CSCE 681 §? 0.60, CSCE 632 §? 0.58, CSCE 629 §? 0.57, ISEN 441 §? 0.57, CSCE 632 §? 0.55, CSCE 629 §? 0.55, CSCE 681 §? 0.54</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yes, there are Texas A&amp;M University courses where the final grade is not solely based on a straightforward calculated average of all components. This often involves policies designed to offer flexibility or to incorporate qualitative assessments beyond raw scores.
+Based on the provided syllabi, here are examples of such courses:
+*   **CSCE 681 (Spring 2026)**: Your final grade is determined by the statistical mean of the top 75% of your individual quiz grades. This means the lowest 25% of your quiz grades do not count, regardless of whether you completed them or not, offering flexibility for a few low scores or missed unexcused lectures [Source 1, 2, 3, 4, 10].
+*   **CSCE 629 (Spring 2026)**: This course drops your lowest grade in the quizzes and exercises component, as well as your lowest homework grade [Source 6, 9]. Additionally, a slight curve might be applied if the course average is low [Source 6].
+*   **CSCE 632 (Spring 2026)**: This course incorporates peer grading for certain assignments (e.g., presentations, team projects). Your score is based on peer evaluations as well as your own evaluation of other student assignments. You can lose points for grading significantly differently than your peers or for giving all students the same scores. The instructor can also modify your score with a multiplier based on team peer evaluations, which can adjust your final project score [Source 5, 8].
+These examples illustrate that grading policies can include mechanisms like dropping low grades, applying curves, or incorporating peer assessment and instructor discretion to determine the final grade, moving beyond a simple arithmetic average of all submitted work.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.61, CSCE 681 §? 0.60, CSCE 629 §? 0.57, ISEN 632 §? 0.57, CSCE 314 §? 0.56</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.62, CSCE 681 §? 0.61, CSCE 681 §? 0.61, CSCE 681 §? 0.60, CSCE 629 §? 0.58</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="86.40000000000001" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -1670,6 +2190,26 @@
           <t>CSCE 672 §? 0.75, CSCE 672 §? 0.75, CSCE 672 §? 0.73, CSCE 672 §? 0.70</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.75, CSCE 672 §? 0.73, CSCE 672 §? 0.70</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The provided context only contains details for CSCE 672, section 600, for Spring 2026 [Source 1, 2, 3, 4].</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.75, CSCE 672 §? 0.73, CSCE 672 §? 0.71, CSCE 672 §? 0.70</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>CSCE 672 §? 0.75, CSCE 672 §? 0.75, CSCE 672 §? 0.73, CSCE 672 §? 0.71, CSCE 672 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="86.40000000000001" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1730,6 +2270,31 @@
           <t>CSCE 629 §? 0.61, CSCE 629 §? 0.59, ISEN 441 §? 0.58, CSCE 629 §? 0.58, CSCE 652 §? 0.56</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.59, ISEN 441 §? 0.58, CSCE 652 §? 0.56</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>I cannot find information in the provided context about how "most" TAMU courses provide e-books or a general policy on whether students usually have to search the library themselves.
+However, based on the provided course materials, required e-books for specific courses are often made available through the Texas A&amp;M University Libraries, sometimes with a direct URL provided for access [Source 1, Source 2, Source 3]. For example:
+*   For CSCE 629, the textbook "Introduction to Algorithms" is "Freely available as an ebook from our library" with a direct URL [Source 1].
+*   For CSCE 652, "Practical Malware Analysis" is accessible "for free at the URL" thanks to the support of Texas A&amp;M University Libraries [Source 3].
+*   For ISEN 441, "An Introduction to Reliability and Maintainability Engineering" is listed as an "E-book available through TAMU library" [Source 2].
+I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ISEN 441 §? 0.58, ISEN 441 §? 0.55, CSCE 222 §? 0.52</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.59, ISEN 441 §? 0.58, CSCE 629 §? 0.58, CSCE 652 §? 0.56</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="100.8" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -1790,6 +2355,32 @@
           <t>CSCE 638 §? 0.71, CSCE 638 §? 0.71, CSCE 638 §? 0.70, CSCE 670 §? 0.70, CSCE 638 §? 0.68, CSCE 638 §? 0.68</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.71, CSCE 638 §? 0.71, CSCE 638 §? 0.70, CSCE 670 §? 0.70, CSCE 638 §? 0.68, CSCE 638 §? 0.68</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following courses cover advanced topics in AI like transformers and large language models:
+*   **CSCE 638 (Spring 2026)** covers these topics extensively, including:
+    *   Transformers [Source 1, 3, 5, 6, 2]
+    *   Contextualized Representations, Pre-Training, Large Language Models [Source 1, 3, 5, 6, 2]
+    *   Large Reasoning Models [Source 1, 3, 5, 2]
+    *   Retrieval-Augmented Generation, Agents [Source 1, 3, 5, 2]
+    *   Multilingual Language Models, Vision-Language Models [Source 1, 3, 5, 2]
+*   **CSCE 670 (Spring 2026)** also includes these topics:
+    *   Transformer; BERT-Based Ranking [Source 4]
+    *   Large Language Models Basics [Source 4]
+    *   Large Language Models with Search Engines [Source 4]
+    *   Large Language Models for Ranking and Recommendation [Source 4]</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>CSCE 638 §? 0.72, CSCE 638 §? 0.71, CSCE 638 §? 0.71, CSCE 638 §? 0.70, CSCE 670 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="129.6" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -1850,6 +2441,28 @@
           <t>CSCE 681 §? 0.75, CSCE 681 §? 0.69</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.75, CSCE 681 §? 0.69</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>I cannot find information about other Texas A&amp;M University CS courses in the provided context.
+However, the CSCE 681 Seminar course itself is specifically designed to help students develop these skills. Its learning outcomes state that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2]. The course's purpose is "to expose students to a broad range of current and seminal research topics in computer science and related fields" [Source 1, Source 2].
+I don't have enough data to recommend other courses accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.75, CSCE 681 §? 0.75, CSCE 681 §? 0.75</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.75, CSCE 681 §? 0.75, CSCE 681 §? 0.69, CSCE 681 §? 0.67, CSCE 681 §? 0.66</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="144" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -1910,6 +2523,37 @@
           <t>CSCE 635 §? 0.57, CSCE 656 §? 0.55, CSCE 421 §? 0.54, CSCE 633 §? 0.52, CSCE 633 §? 0.52, CSCE 672 §? 0.51, CSCE 672 §? 0.51, CSCE 672 §? 0.51, CSCE 672 §? 0.50, CSCE 633 §? 0.50</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>CSCE 635 §? 0.57, CSCE 421 §? 0.54, CSCE 633 §? 0.52, CSCE 672 §? 0.51, CSCE 633 §? 0.50, CSCE 752 §? 0.49, CSCE 752 §? 0.47, CSCE 648 §? 0.45, CSCE 748 §? 0.45, CSCE 614 §? 0.44</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>The principle underlying effective management of end-of-semester workload is **proactive academic planning and resource utilization**. This involves understanding the scope and deadlines of all major deliverables, breaking down large tasks, and leveraging available support or policies to mitigate stress and ensure timely submission.
+Based on the provided course information for Spring 2026, several strategies can be inferred for managing the end-of-semester workload at Texas A&amp;M University:
+1.  **Early Planning and Schedule Awareness:** Many final projects, reports, and exams are due in late April and early May across different courses. For example, CSCE 635 has Final Project Presentations from April 17-22 and a Final Project Report due April 27 [Source 1]. CSCE 672 has Final Project Presentations due April 27-28 and reports due May 1 [Source 4]. CSCE 748's final project report is due April 30 [Source 9], while CSCE 633 and CSCE 421 have final projects due May 4 and May 5, respectively [Source 3, 5, 2]. CSCE 752 has a Final Exam on May 1 [Source 6, 7]. Students should "plan their time" accordingly, as advised in CSCE 752 [Source 6, 7].
+2.  **Utilize Intermediate Deliverables:** Several courses incorporate project proposals or check-ins throughout the semester. CSCE 635 requires a project proposal by January 30 and a midterm project check-in by March 2-4 [Source 1]. CSCE 748 students propose their projects mid-semester [Source 9], and CSCE 614 also includes a project proposal [Source 10]. These intermediate steps can help students break down large projects, receive early feedback, and manage their progress, preventing a last-minute rush.
+3.  **Proactive Communication with Instructors:** If difficulties arise in completing assignments, students are advised to "contact the TA or the instructor before the deadline" [Source 10]. This can be crucial for discussing potential extensions or support.
+4.  **Understand and Leverage Late Work Policies:** Late work policies vary significantly by course.
+    *   Some courses, like CSCE 748, offer a limited number of "granted late days" (e.g., 5 days for the entire course, though not for the final project) [Source 9].
+    *   Others apply penalties, such as CSCE 648, where projects submitted after the deadline are graded at 50% of the actual score [Source 8], or CSCE 752, where scores decrease significantly after the deadline [Source 7].
+    *   CSCE 421 explicitly states, "No Late Assignments will be accepted" [Source 2].
+    Familiarizing oneself with these policies for each course can help prioritize tasks and make informed decisions about when to use available flexibility.
+5.  **Leverage Academic Resources:** Some courses mention specific resources, such as TAMU HPRC access for implementing assignments [Source 2, 3, 5]. Knowing about and utilizing these resources can aid in project completion.
+I don't have enough data to provide a comprehensive list of all possible strategies based on the available syllabi, as they primarily focus on specific course schedules and policies rather than general academic advice.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CSCE 635 §? 0.57, CSCE 633 §? 0.52</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>CSCE 635 §? 0.57, CSCE 421 §? 0.54, CSCE 633 §? 0.52, CSCE 633 §? 0.50, CSCE 752 §? 0.49</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="86.40000000000001" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -1970,6 +2614,26 @@
           <t>CSCE 679 §? 0.81, CSCE 679 §? 0.81, CSCE 679 §? 0.80, CSCE 679 §? 0.77</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>CSCE 679 §? 0.81, CSCE 679 §? 0.81, CSCE 679 §? 0.80, CSCE 679 §? 0.77</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The context only details the grading policy for CSCE 679, which includes a project using D3.js for graduate students that accounts for 50% of the final grade [1, 2, 3, 4]. It does not provide information about grading policies or project structures in other TAMU graduate CS courses.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CSCE 679 §? 0.81, CSCE 679 §? 0.81, CSCE 679 §? 0.80, CSCE 679 §? 0.79, CSCE 447 §? 0.79</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>CSCE 679 §? 0.81, CSCE 679 §? 0.81, CSCE 679 §? 0.80, CSCE 679 §? 0.79, CSCE 679 §? 0.77</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28.8" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -2028,6 +2692,26 @@
       <c r="N25" t="inlineStr">
         <is>
           <t>CSCE 629 §? 0.78, CSCE 629 §? 0.70, CSCE 629 §? 0.57, CSCE 629 §? 0.55</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.77, CSCE 629 §? 0.72</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629 section 600 in Spring 2026 is scheduled for Thursday, February 26, in class [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.77, CSCE 629 §? 0.75, CSCE 629 §? 0.70</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>CSCE 629 §? 0.75, CSCE 629 §? 0.57</t>
         </is>
       </c>
     </row>
@@ -2096,6 +2780,26 @@
           <t>CSCE 608 §? 0.73, CSCE 608 §? 0.56</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.77, CSCE 608 §? 0.55</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009 (ISBN: 978-0-13-187325-4) [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.89, CSCE 608 §? 0.42</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.89, CSCE 608 §? 0.42</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="43.2" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -2154,6 +2858,26 @@
       <c r="N27" t="inlineStr">
         <is>
           <t>CSCE 633 §? 0.75, CSCE 633 §? 0.47</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.75, CSCE 633 §? 0.44</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS Unix hosts or other public systems in the department lab [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.72, CSCE 633 §? 0.71, CSCE 633 §? 0.71</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.71, CSCE 633 §? 0.47</t>
         </is>
       </c>
     </row>
@@ -2218,6 +2942,30 @@
       <c r="N28" t="inlineStr">
         <is>
           <t>CSCE 633 §? 0.76, CSCE 633 §? 0.60</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.75, CSCE 633 §? 0.58</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 1].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 1].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.85, CSCE 633 §? 0.84, CSCE 633 §? 0.83</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>CSCE 633 §? 0.84, CSCE 633 §? 0.57</t>
         </is>
       </c>
     </row>
@@ -2286,6 +3034,39 @@
           <t>CSCE 665 §? 0.80, CSCE 665 §? 0.75</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.77, CSCE 665 §? 0.72, CSCE 665 §? 0.70, CSCE 665 §? 0.62</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CSCE 665, section 600, titled "Advanced Networking and Security," covers security aspects of various network protocols, including investigation and tool development using "live" machines and networks [Source 1].
+The course introduces modern topics in computer and network security, providing a thorough grounding for students interested in research or real-world security issues. Key topics may include [Source 3]:
+*   **Basic network &amp; system security:** software security, malware, botnet, intrusion detection.
+*   **Security in a software-defined world:** SDN/NFV, Cloud, 5G/Edge, Vehicle security.
+*   **Mobile &amp; IoT security:** smartphone security, Alexa and voice app security.
+*   **Web and Web3 security:** traditional web security, spam, Web3 (DeFi, blockchain) security.
+*   **AI/LLM security:** LLM-based security, adversarial learning/backdoor, advanced applications with AI [Source 2].
+The course schedule outlines topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 4].
+**Prerequisites:** Graduate classification and approval of the instructor [Source 1, 2].
+**Learning Outcomes:** Upon completion, students will be able to [Source 2]:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks.
+*   Synthesize fundamental security principles and mechanisms to design robust defenses.
+*   Critique state-of-the-art security literature.
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.89, CSCE 665 §? 0.68</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.89, CSCE 665 §? 0.68</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="144" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -2350,6 +3131,31 @@
           <t>CSCE 669 §? 0.71, CSCE 669 §? 0.66</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.70, CSCE 669 §? 0.57</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>After completing CSCE 669, Computational Optimization, you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 1].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 1].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems, with applications to max flow, matching, and matroids [Source 2]. The ability to apply these theories to real-world problems and conduct advanced research in computational optimization directly relates to careers in fields requiring complex problem-solving, algorithm design, and data analysis, such as software development, data science, operations research, and academic research [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.84, CSCE 669 §? 0.54</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.84, CSCE 669 §? 0.54</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="144" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -2414,6 +3220,30 @@
           <t>CSCE 665 §? 0.76, CSCE 665 §? 0.71, CSCE 665 §? 0.64</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.76, CSCE 665 §? 0.62</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665, students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 1].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 1].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 1].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.83, CSCE 665 §? 0.71</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>CSCE 665 §? 0.83, CSCE 665 §? 0.71</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="57.6" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -2474,6 +3304,26 @@
           <t>CSCE 608 §? 0.88, CSCE 608 §? 0.70</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.88, CSCE 608 §? 0.69</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas [Source 2]. Students should check Canvas daily for announcements, course material, and due dates [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.90, CSCE 608 §? 0.66</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>CSCE 608 §? 0.90, CSCE 608 §? 0.66</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="72" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -2532,6 +3382,33 @@
       <c r="N33" t="inlineStr">
         <is>
           <t>CSCE 681 §? 0.72, CSCE 681 §? 0.70</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.71, CSCE 681 §? 0.61, CSCE 681 §? 0.50</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681, Section 600, regarding preparing reports and discussing research, appear attainable based on the course structure.
+The course's purpose is to expose students to a broad range of current and seminal research topics in computer science. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1].
+To achieve this, students are expected to:
+*   Attend all lectures [Source 1, 3].
+*   Write a report for each lecture [Source 1, 3].
+*   These reports are structured as Canvas quizzes, requiring students to analyze and summarize research by including sections such as background, problem statement, proposed solution, results, and critique [Source 3].
+*   Students must achieve an average score of 80% or higher to pass the course [Source 1].
+The regular practice of attending lectures on research topics and consistently writing structured reports for each, along with the grading requirement, directly supports the development of skills in preparing reports and discussing research [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.85, CSCE 681 §? 0.84</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>CSCE 681 §? 0.85, CSCE 681 §? 0.49</t>
         </is>
       </c>
     </row>
@@ -2598,6 +3475,39 @@
           <t>CSCE 611 §? 0.79, CSCE 611 §? 0.74, CSCE 611 §? 0.69, CSCE 611 §? 0.68, CSCE 611 §? 0.68</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.80, CSCE 611 §? 0.73, CSCE 611 §? 0.70, CSCE 611 §? 0.67, CSCE 611 §? 0.66, CSCE 611 §? 0.61</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, "Operating Systems," is offered in Spring 2026 [Source 4].
+**Course Purpose and Overview:**
+This course provides an overview of the general architecture and key components of modern operating systems. It reviews computer architecture hardware/software evolution, basic operating systems concepts, methods of OS design and construction, and algorithms for CPU scheduling, memory, and general resource allocation. It also covers process coordination and management, case studies of several operating systems, and their quality-of-services and impact on applications [Source 4, 2]. Students will leverage knowledge from Computer Architecture and Computer Systems to understand and implement aspects of operating systems, such as memory management, persistent storage and file systems, threading, scheduling, and resource management. The course also covers fundamental approaches to virtualization and building distributed systems [Source 2, 3].
+**Prerequisites:**
+The prerequisites for CSCE 611 are CSCE 313 and graduate classification [Source 3, 2].
+**Key Topics and Early Weeks:**
+The course covers topics including memory management, persistent storage and file systems, threading, scheduling, and resource management [Source 2, 3].
+Specifically, the early weeks of the course cover:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 1].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 1].
+*   **Week 3:** Memory: Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 1].
+*   **Week 4:** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 1].
+*   **Week 5:** Page Replacement Policies I and II, and Recursive Page Table Lookup [Source 1].
+I cannot find information regarding the grading breakdown in the provided context.</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.79, CSCE 611 §? 0.79, CSCE 611 §? 0.77, CSCE 611 §? 0.77, CSCE 611 §? 0.71</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>CSCE 611 §? 0.79, CSCE 611 §? 0.77, CSCE 611 §? 0.70</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="244.8" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -2660,6 +3570,55 @@
       <c r="N35" t="inlineStr">
         <is>
           <t>CSCE 670 §? 0.68, CSCE 670 §? 0.65, CSCE 670 §? 0.59</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.70, CSCE 670 §? 0.68</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>For CSCE 670, section 600 in Spring 2026, effective time management will involve balancing five programming assignments, four quizzes, a significant group project, and a final exam.
+Here's a breakdown of the components and their deadlines to help you plan:
+**Grading Breakdown** [Source 2]:
+*   **Homework:** 30%
+*   **Quizzes:** 20%
+*   **Group Project:** 20%
+*   **Final Exam:** 30%
+**Key Dates and Planning Considerations:**
+*   **Homeworks (30% total)**: There are five programming assignments, all in Python, with the first being an introduction to Jupyter Notebook. These are individual assignments, but discussion of approaches is encouraged [Source 2].
+    *   Homework 0: due Jan 26 [Source 1]
+    *   Homework 1: due Feb 9 [Source 1]
+    *   Homework 2: due Mar 2 [Source 1]
+    *   Homework 3: due Mar 30 [Source 1]
+    *   Homework 4: due Apr 20 [Source 1]
+    *   *Planning Tip:* Homeworks are spread throughout the semester, with increasing weight (2% for HW0, 7% for others). Start early on each to allow time for debugging and understanding the concepts.
+*   **Quizzes (20% total)**: Four brief in-class quizzes [Source 2].
+    *   Quiz 1: Feb 6 [Source 1]
+    *   Quiz 2: Feb 27 [Source 1]
+    *   Quiz 3: Mar 25 [Source 1]
+    *   Quiz 4: Apr 15 [Source 1]
+    *   *Planning Tip:* These are in-class, so regular attendance and keeping up with weekly material will be crucial for success.
+*   **Group Project (20% total)**: You will work in teams of 3 or 4 on a mini-research project [Source 2].
+    *   Proposal: due Mar 7 [Source 1]
+    *   Presentation: Apr 20, Apr 22, Apr 24, and Apr 27 classes [Source 1]
+    *   Report: due May 2 [Source 1]
+    *   *Planning Tip:* The project spans a significant portion of the semester. Begin forming your group and brainstorming ideas early. The proposal is due in early March, and the presentations and final report are due at the very end of the semester, requiring consistent effort.
+*   **Final Exam (30% total)**: A comprehensive final exam [Source 2].
+    *   Date: May 4, 3:30 - 5:30 PM in HRBB 113 [Source 2]
+    *   *Planning Tip:* Given its weight, allocate dedicated study time for the final exam, reviewing all course material.
+To effectively plan your time, regularly check the course schedule for upcoming deadlines and allocate consistent time each week for coursework, especially for the programming assignments and group project. The course covers topics like word2vec, Neural Ranking, Transformers, BERT-Based Ranking, Neural Collaborative Filtering, and Large Language Models [Source 1], so understanding these concepts will be key to success in all graded components.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.69, CSCE 670 §? 0.64</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.69, CSCE 670 §? 0.64</t>
         </is>
       </c>
     </row>
@@ -2728,6 +3687,52 @@
           <t>CSCE 632 §? 0.73, CSCE 632 §? 0.71, CSCE 632 §? 0.69, CSCE 632 §? 0.65</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>CSCE 632 §? 0.78, CSCE 632 §? 0.71, CSCE 632 §? 0.68, CSCE 632 §? 0.66, CSCE 632 §? 0.61</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>For CSCE 632, Section 600, in Spring 2026, final grades are determined by a combination of graded components and a specific grading scale [Source 1, 2, 3, 4, 5].
+**Graded Components and Weighting:**
+*   **Pre-Class Engagement:** 5% [Source 3]
+    *   Includes course readings, quizzes, polls, and surveys. Credit is given for submissions prior to class [Source 3].
+*   **Quick Applications:** 20% [Source 4]
+    *   Timed assignments designed for quick application of class materials, typically taking 15-20 minutes with at least 45 minutes provided [Source 4].
+*   **Literature Review:** 10% [Source 4]
+    *   Students compile a literature review on an accessibility topic, including at least 10 related peer-reviewed papers, themes, gaps, and an annotated bibliography [Source 4].
+*   **Current Research Presentation:** 5% [Source 4]
+    *   Based on the student's Literature Review and is peer-graded [Source 1, 4]. Scores are based on peer evaluations and the student's evaluation of other assignments. Points can be lost for grading significantly differently than peers or giving all students the same scores [Source 1].
+*   **Team Project:** 25% [Source 1]
+    *   Students work in groups to address a barrier for people with disabilities by designing and implementing a technology-based solution. The barrier must be instructor-approved [Source 1]. Parts of this project are peer-graded, with scores based on peer evaluations and the student's evaluation of other assignments [Source 1, 2]. The instructor may establish and modify a multiplier based on team peer evaluations, which can affect individual scores [Source 2].
+**Grading Policies:**
+*   **Graded Work Modifications:** Challenges to grading must be made within one week of grade publication. The instructor reserves the right to audit grades, which can result in increasing or decreasing already released scores [Source 3].
+*   **Peer Grading:** For assignments like the Current Research Presentation and parts of the Team Project, scores are based on peer evaluations and your evaluation of other student assignments. You can lose points for grading significantly differently than your peers or giving all students the same scores, emphasizing critical grading [Source 1, 2].
+*   **Instructor Modifications:** The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can lead to letter grade reductions even if a zero would mathematically result in a higher letter grade [Source 5].
+*   **Late Work Policy:** Penalties for unexcused late submissions are 5% per calendar day. Makeup work for excused absences is exempt from this policy [Source 5].
+**Grading Scale:**
+Grades will be rounded to the nearest whole number and assigned according to the following scale [Source 2, 5]:
+| Grade | Score     | Achievement |
+| :---- | :-------- | :---------- |
+| A     | ≥ 90      | Excellent   |
+| B     | &lt; 90 and ≥ 80 | Good        |
+| C     | &lt; 80 and ≥ 70 | Satisfactory|
+| D     | &lt; 70 and ≥ 60 | Passing     |
+| F     | &lt; 60      | Failing     |
+[Source 2, 5]</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CSCE 632 §? 0.75, CSCE 632 §? 0.74, CSCE 632 §? 0.70, CSCE 632 §? 0.68</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>CSCE 632 §? 0.75, CSCE 632 §? 0.74, CSCE 632 §? 0.70, CSCE 632 §? 0.68</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="201.6" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -2792,6 +3797,34 @@
           <t>CSCE 669 §? 0.78, CSCE 669 §? 0.55</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.77, CSCE 669 §? 0.60</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>For CSCE 669, section 600, your overall grade is determined by the following components [Source 1]:
+*   **Homework:** 30% (3 assignments, 10% each, testing understanding of lectures)
+*   **Course Project:** 35% (provides opportunities to read recent papers and do research)
+*   **Final Exam:** 35% (comprehensive)
+The grading scale is as follows [Source 1, 2]:
+*   **A:** 90-100%
+*   **B:** 70-89%
+*   **C:** 60-70%
+*   **F:** 0-59%</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.77, CSCE 669 §? 0.57</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>CSCE 669 §? 0.77, CSCE 669 §? 0.57</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="259.2" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -2854,6 +3887,33 @@
       <c r="N38" t="inlineStr">
         <is>
           <t>CSCE 670 §? 0.80, CSCE 670 §? 0.56</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.80, CSCE 670 §? 0.59</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, titled "Information Storage and Retrieval," covers the representation, storage, and access to very large multimedia document collections [Source 1].
+Key topics include:
+*   **Fundamental data structures and algorithms** of information storage and retrieval systems [Source 1].
+*   **Algorithms for indexing, compressing, and querying** very large collections [Source 1].
+*   **Web search concepts and models**, such as text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 2].
+*   **Recommender systems concepts and models**, including collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 2].
+Upon completion, students will be able to define and explain these concepts and models, and design, implement, and evaluate core algorithms for web search and recommendation systems [Source 2].
+The prerequisites for this course are CSCE 310 or CSCE 603, or approval of the instructor, along with graduate classification [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.82, CSCE 670 §? 0.57</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>CSCE 670 §? 0.82, CSCE 670 §? 0.57</t>
         </is>
       </c>
     </row>
